--- a/xls/square_16_tri3_21.xlsx
+++ b/xls/square_16_tri3_21.xlsx
@@ -482,13 +482,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-2.5638450537521074</v>
+        <v>-2.5638430941669146</v>
       </c>
       <c r="J21">
-        <v>-2.0651104593632614</v>
+        <v>-2.0651106358368536</v>
       </c>
       <c r="K21">
-        <v>1.189345975256</v>
+        <v>1.1893553599498206</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-2.392954056747244</v>
+        <v>-2.392956325912857</v>
       </c>
       <c r="J22">
-        <v>-1.9309903686358023</v>
+        <v>-1.9309900671819364</v>
       </c>
       <c r="K22">
-        <v>1.8502521980678264</v>
+        <v>1.8502521555884393</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-2.0468416634670783</v>
+        <v>-2.0468411725107023</v>
       </c>
       <c r="J23">
-        <v>-1.6716261811674942</v>
+        <v>-1.6716264633651685</v>
       </c>
       <c r="K23">
-        <v>3.11245053477808</v>
+        <v>3.112450570304346</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-1.5854055785443142</v>
+        <v>-1.5854051951868162</v>
       </c>
       <c r="J24">
-        <v>-1.283517205470152</v>
+        <v>-1.2835170574749106</v>
       </c>
       <c r="K24">
-        <v>3.4568411396963423</v>
+        <v>3.4568411292793955</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.497125471728105</v>
+        <v>-0.4971254943887092</v>
       </c>
       <c r="J25">
-        <v>-0.33978642729158187</v>
+        <v>-0.3397864383452448</v>
       </c>
       <c r="K25">
-        <v>3.759897547023584</v>
+        <v>3.7598975598282878</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00011288946664156317</v>
+        <v>-0.00011288938711821861</v>
       </c>
       <c r="J26">
-        <v>-0.0011534286871804941</v>
+        <v>-0.0011534286422307972</v>
       </c>
       <c r="K26">
-        <v>3.111897488900709</v>
+        <v>3.1118974865315505</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.004091677807462235</v>
+        <v>-0.004091677805312504</v>
       </c>
       <c r="J27">
-        <v>-0.003415291710241051</v>
+        <v>-0.0034152917087231223</v>
       </c>
       <c r="K27">
-        <v>3.1617669505802213</v>
+        <v>3.161766950621287</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0032171321015505676</v>
+        <v>-0.0032171320993932603</v>
       </c>
       <c r="J28">
-        <v>-0.0030035870858929675</v>
+        <v>-0.0030035870845911694</v>
       </c>
       <c r="K28">
-        <v>3.172569685297426</v>
+        <v>3.1725696853085483</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>0.0007392401624761243</v>
+        <v>0.0007392401627026446</v>
       </c>
       <c r="J29">
-        <v>0.00017086115710596286</v>
+        <v>0.0001708611572575919</v>
       </c>
       <c r="K29">
-        <v>2.7585812910272036</v>
+        <v>2.7585812911968097</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.000859224585849721</v>
+        <v>-0.0008592245884123754</v>
       </c>
       <c r="J30">
-        <v>-0.0006126511814421326</v>
+        <v>-0.0006126511830505355</v>
       </c>
       <c r="K30">
-        <v>2.70150492154518</v>
+        <v>2.7015049222323313</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>7.79119263029047e-6</v>
+        <v>7.791192638101382e-6</v>
       </c>
       <c r="J31">
-        <v>-1.5935085938944508e-5</v>
+        <v>-1.593508593450844e-5</v>
       </c>
       <c r="K31">
-        <v>2.2777178196087067</v>
+        <v>2.2777178197705803</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -867,13 +867,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.0004198152583758423</v>
+        <v>-0.0004198152582566327</v>
       </c>
       <c r="J32">
-        <v>-0.0003355152019133304</v>
+        <v>-0.00033551520183520777</v>
       </c>
       <c r="K32">
-        <v>2.630525267632449</v>
+        <v>2.6305252673871866</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_21.xlsx
+++ b/xls/square_16_tri3_21.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>484</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>289</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>2.1964932890601356</v>
+      </c>
+      <c r="J19">
+        <v>-1.0910518706546868</v>
+      </c>
+      <c r="K19">
+        <v>2.981611366129628</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>484</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>289</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>0.2897267161646791</v>
+      </c>
+      <c r="J20">
+        <v>-1.9943078603877595</v>
+      </c>
+      <c r="K20">
+        <v>1.6401921016533045</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
